--- a/Compititor's_Price/Core-Products_Prices/Core-Products_Prices_20-06-2025.xlsx
+++ b/Compititor's_Price/Core-Products_Prices/Core-Products_Prices_20-06-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Core-Products_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F68F10C-F83B-4E7F-81D2-83F59B1A6C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B3A5DF7-CB21-4401-88B9-4DD734497666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1438,12 +1438,14 @@
   <dimension ref="A1:J46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="64.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="123" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.42578125" customWidth="1"/>
     <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20.140625" bestFit="1" customWidth="1"/>
   </cols>
